--- a/sheets/민요/검수/쑥대머리.xlsx
+++ b/sheets/민요/검수/쑥대머리.xlsx
@@ -4,15 +4,14 @@
   <sheets>
     <sheet name="정보" sheetId="1" r:id="rId1"/>
     <sheet name="정간목록" sheetId="2" r:id="rId2"/>
-    <sheet name="악보 1" sheetId="3" r:id="rId3"/>
-    <sheet name="악보 2" sheetId="4" r:id="rId4"/>
+    <sheet name="악보" sheetId="3" r:id="rId3"/>
   </sheets>
 </workbook>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <fonts count="2">
+  <fonts count="6">
     <font>
       <sz val="11"/>
       <name val="맑은 고딕"/>
@@ -21,6 +20,26 @@
     <font>
       <b/>
       <sz val="11"/>
+      <name val="맑은 고딕"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="14"/>
+      <name val="맑은 고딕"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="14"/>
+      <name val="맑은 고딕"/>
+    </font>
+    <font>
+      <sz val="22"/>
+      <name val="맑은 고딕"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="13"/>
       <name val="맑은 고딕"/>
       <family val="2"/>
     </font>
@@ -51,7 +70,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="6">
     <border>
       <left/>
       <right/>
@@ -74,11 +93,71 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top style="thin">
+        <color auto="1"/>
+      </top>
+      <bottom style="thin">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top style="thin">
+        <color auto="1"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FFFFFFFF"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top style="thin">
+        <color rgb="FFFFFFFF"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FFFFFFFF"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top style="thin">
+        <color rgb="FFFFFFFF"/>
+      </top>
+      <bottom style="thin">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="24">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -97,6 +176,57 @@
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1" applyFont="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1" applyFont="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1" applyFont="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1" applyFont="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -5131,8 +5261,12 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <pageSetUpPr fitToPage="0"/>
+  </sheetPr>
+  <dimension ref="A1:Q28"/>
   <cols>
-    <col min="1" max="1" width="6" customWidth="1"/>
+    <col min="1" max="1" width="2" customWidth="1"/>
     <col min="2" max="2" width="9" customWidth="1"/>
     <col min="3" max="3" width="6" customWidth="1"/>
     <col min="4" max="4" width="9" customWidth="1"/>
@@ -5151,1446 +5285,1298 @@
     <col min="17" max="17" width="6" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1">
-      <c r="A1" s="6" t="inlineStr">
-        <is>
-          <t xml:space="preserve">쑥대머리 — 민요채보-1/쑥대머리.png</t>
-        </is>
-      </c>
-      <c r="B1" s="6"/>
-      <c r="C1" s="6"/>
-      <c r="D1" s="6"/>
-      <c r="E1" s="6"/>
-      <c r="F1" s="6"/>
-      <c r="G1" s="6"/>
-      <c r="H1" s="6"/>
-      <c r="I1" s="6"/>
-      <c r="J1" s="6"/>
-      <c r="K1" s="6"/>
-      <c r="L1" s="6"/>
-      <c r="M1" s="6"/>
-      <c r="N1" s="6"/>
-      <c r="O1" s="6"/>
-      <c r="P1" s="6"/>
-      <c r="Q1" s="6"/>
-    </row>
-    <row r="2">
-      <c r="A2" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">정간</t>
-        </is>
-      </c>
-      <c r="B2" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">8줄</t>
-        </is>
-      </c>
-      <c r="C2" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">가사</t>
-        </is>
-      </c>
-      <c r="D2" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">7줄</t>
-        </is>
-      </c>
-      <c r="E2" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">가사</t>
-        </is>
-      </c>
-      <c r="F2" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">6줄</t>
-        </is>
-      </c>
-      <c r="G2" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">가사</t>
-        </is>
-      </c>
-      <c r="H2" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">5줄</t>
-        </is>
-      </c>
-      <c r="I2" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">가사</t>
-        </is>
-      </c>
-      <c r="J2" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">4줄</t>
-        </is>
-      </c>
-      <c r="K2" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">가사</t>
-        </is>
-      </c>
-      <c r="L2" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">3줄</t>
-        </is>
-      </c>
-      <c r="M2" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">가사</t>
-        </is>
-      </c>
-      <c r="N2" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">2줄</t>
-        </is>
-      </c>
-      <c r="O2" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">가사</t>
-        </is>
-      </c>
-      <c r="P2" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1줄</t>
-        </is>
-      </c>
-      <c r="Q2" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">가사</t>
-        </is>
-      </c>
-    </row>
-    <row r="3" ht="30" customHeight="1">
-      <c r="A3" s="1">
-        <v>1</v>
-      </c>
-      <c r="B3" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">南</t>
-        </is>
-      </c>
-      <c r="C3" s="2" t="inlineStr">
+    <row r="1"/>
+    <row r="2" ht="60" customHeight="1">
+      <c s="8" t="inlineStr" r="B2">
+        <is>
+          <t xml:space="preserve">쑥대머리</t>
+        </is>
+      </c>
+      <c s="8" r="C2"/>
+      <c s="8" r="D2"/>
+      <c s="8" r="E2"/>
+      <c s="8" r="F2"/>
+      <c s="8" r="G2"/>
+      <c s="8" r="H2"/>
+      <c s="8" r="I2"/>
+      <c s="8" r="J2"/>
+      <c s="8" r="K2"/>
+      <c s="8" r="L2"/>
+      <c s="8" r="M2"/>
+      <c s="8" r="N2"/>
+      <c s="8" r="O2"/>
+      <c s="8" r="P2"/>
+      <c s="8" r="Q2"/>
+    </row>
+    <row r="3" ht="56" customHeight="1">
+      <c r="B3" s="16" t="inlineStr">
+        <is>
+          <t xml:space="preserve">南</t>
+        </is>
+      </c>
+      <c r="C3" s="18" t="inlineStr">
         <is>
           <t xml:space="preserve">키</t>
         </is>
       </c>
-      <c r="D3" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">潕</t>
-        </is>
-      </c>
-      <c r="E3" s="2" t="inlineStr">
+      <c r="D3" s="16" t="inlineStr">
+        <is>
+          <t xml:space="preserve">潕</t>
+        </is>
+      </c>
+      <c r="E3" s="18" t="inlineStr">
         <is>
           <t xml:space="preserve">겨</t>
         </is>
       </c>
-      <c r="F3" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">南</t>
-        </is>
-      </c>
-      <c r="G3" s="2" t="inlineStr">
+      <c r="F3" s="16" t="inlineStr">
+        <is>
+          <t xml:space="preserve">南</t>
+        </is>
+      </c>
+      <c r="G3" s="18" t="inlineStr">
         <is>
           <t xml:space="preserve">일</t>
         </is>
       </c>
-      <c r="H3" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">潕</t>
-        </is>
-      </c>
-      <c r="I3" s="2" t="inlineStr">
+      <c r="H3" s="16" t="inlineStr">
+        <is>
+          <t xml:space="preserve">潕</t>
+        </is>
+      </c>
+      <c r="I3" s="18" t="inlineStr">
         <is>
           <t xml:space="preserve">오</t>
         </is>
       </c>
-      <c r="J3" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">潕</t>
-        </is>
-      </c>
-      <c r="K3" s="2" t="inlineStr">
+      <c r="J3" s="16" t="inlineStr">
+        <is>
+          <t xml:space="preserve">潕</t>
+        </is>
+      </c>
+      <c r="K3" s="18" t="inlineStr">
         <is>
           <t xml:space="preserve">보</t>
         </is>
       </c>
-      <c r="L3" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">南</t>
-        </is>
-      </c>
-      <c r="M3" s="2" t="inlineStr">
+      <c r="L3" s="16" t="inlineStr">
+        <is>
+          <t xml:space="preserve">南</t>
+        </is>
+      </c>
+      <c r="M3" s="18" t="inlineStr">
         <is>
           <t xml:space="preserve">생</t>
         </is>
       </c>
-      <c r="N3" s="2" t="inlineStr">
+      <c r="N3" s="16" t="inlineStr">
         <is>
           <t xml:space="preserve">姑</t>
         </is>
       </c>
-      <c r="O3" s="2" t="inlineStr">
+      <c r="O3" s="18" t="inlineStr">
         <is>
           <t xml:space="preserve">적</t>
         </is>
       </c>
-      <c r="P3" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">潕</t>
-        </is>
-      </c>
-      <c r="Q3" s="2" t="inlineStr">
+      <c r="P3" s="16" t="inlineStr">
+        <is>
+          <t xml:space="preserve">潕</t>
+        </is>
+      </c>
+      <c r="Q3" s="18" t="inlineStr">
         <is>
           <t xml:space="preserve">쑥</t>
         </is>
       </c>
     </row>
-    <row r="4" ht="30" customHeight="1">
-      <c r="A4" s="1">
-        <v>2</v>
-      </c>
-      <c r="B4" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">南</t>
-        </is>
-      </c>
-      <c r="C4" s="2" t="inlineStr">
+    <row r="4" ht="56" customHeight="1">
+      <c r="B4" s="16" t="inlineStr">
+        <is>
+          <t xml:space="preserve">南</t>
+        </is>
+      </c>
+      <c r="C4" s="19" t="inlineStr">
         <is>
           <t xml:space="preserve">신</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">南</t>
-        </is>
-      </c>
-      <c r="E4" s="2"/>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">潕</t>
-        </is>
-      </c>
-      <c r="G4" s="2"/>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">潕</t>
-        </is>
-      </c>
-      <c r="I4" s="2"/>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">潕</t>
-        </is>
-      </c>
-      <c r="K4" s="2"/>
-      <c r="L4" s="2"/>
-      <c r="M4" s="2"/>
-      <c r="N4" s="2"/>
-      <c r="O4" s="2"/>
-      <c r="P4" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">南</t>
-        </is>
-      </c>
-      <c r="Q4" s="2"/>
-    </row>
-    <row r="5" ht="30" customHeight="1">
-      <c r="A5" s="1">
-        <v>3</v>
-      </c>
-      <c r="B5" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">潕</t>
-        </is>
-      </c>
-      <c r="C5" s="2" t="inlineStr">
+      <c r="D4" s="16" t="inlineStr">
+        <is>
+          <t xml:space="preserve">南</t>
+        </is>
+      </c>
+      <c r="E4" s="19"/>
+      <c r="F4" s="16" t="inlineStr">
+        <is>
+          <t xml:space="preserve">潕</t>
+        </is>
+      </c>
+      <c r="G4" s="19"/>
+      <c r="H4" s="16" t="inlineStr">
+        <is>
+          <t xml:space="preserve">潕</t>
+        </is>
+      </c>
+      <c r="I4" s="19"/>
+      <c r="J4" s="16" t="inlineStr">
+        <is>
+          <t xml:space="preserve">潕</t>
+        </is>
+      </c>
+      <c r="K4" s="19"/>
+      <c r="L4" s="16"/>
+      <c r="M4" s="19"/>
+      <c r="N4" s="16"/>
+      <c r="O4" s="19"/>
+      <c r="P4" s="16" t="inlineStr">
+        <is>
+          <t xml:space="preserve">南</t>
+        </is>
+      </c>
+      <c r="Q4" s="19"/>
+    </row>
+    <row r="5" ht="56" customHeight="1">
+      <c r="B5" s="16" t="inlineStr">
+        <is>
+          <t xml:space="preserve">潕</t>
+        </is>
+      </c>
+      <c r="C5" s="20" t="inlineStr">
         <is>
           <t xml:space="preserve">찬</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">·</t>
-        </is>
-      </c>
-      <c r="E5" s="2" t="inlineStr">
+      <c r="D5" s="16" t="inlineStr">
+        <is>
+          <t xml:space="preserve">·</t>
+        </is>
+      </c>
+      <c r="E5" s="20" t="inlineStr">
         <is>
           <t xml:space="preserve">를</t>
         </is>
       </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">潕</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
+      <c r="F5" s="16" t="inlineStr">
+        <is>
+          <t xml:space="preserve">潕</t>
+        </is>
+      </c>
+      <c r="G5" s="20" t="inlineStr">
         <is>
           <t xml:space="preserve">장</t>
         </is>
       </c>
-      <c r="H5" s="2" t="inlineStr">
+      <c r="H5" s="16" t="inlineStr">
         <is>
           <t xml:space="preserve">姑</t>
         </is>
       </c>
-      <c r="I5" s="2" t="inlineStr">
+      <c r="I5" s="20" t="inlineStr">
         <is>
           <t xml:space="preserve">리</t>
         </is>
       </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">潕</t>
-        </is>
-      </c>
-      <c r="K5" s="2" t="inlineStr">
+      <c r="J5" s="16" t="inlineStr">
+        <is>
+          <t xml:space="preserve">潕</t>
+        </is>
+      </c>
+      <c r="K5" s="20" t="inlineStr">
         <is>
           <t xml:space="preserve">고</t>
         </is>
       </c>
-      <c r="L5" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">潕</t>
-        </is>
-      </c>
-      <c r="M5" s="2" t="inlineStr">
+      <c r="L5" s="16" t="inlineStr">
+        <is>
+          <t xml:space="preserve">潕</t>
+        </is>
+      </c>
+      <c r="M5" s="20" t="inlineStr">
         <is>
           <t xml:space="preserve">각</t>
         </is>
       </c>
-      <c r="N5" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">潕</t>
-        </is>
-      </c>
-      <c r="O5" s="2" t="inlineStr">
+      <c r="N5" s="16" t="inlineStr">
+        <is>
+          <t xml:space="preserve">潕</t>
+        </is>
+      </c>
+      <c r="O5" s="20" t="inlineStr">
         <is>
           <t xml:space="preserve">막</t>
         </is>
       </c>
-      <c r="P5" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">南</t>
-        </is>
-      </c>
-      <c r="Q5" s="2" t="inlineStr">
+      <c r="P5" s="16" t="inlineStr">
+        <is>
+          <t xml:space="preserve">南</t>
+        </is>
+      </c>
+      <c r="Q5" s="20" t="inlineStr">
         <is>
           <t xml:space="preserve">대</t>
         </is>
       </c>
     </row>
-    <row r="6" ht="30" customHeight="1">
-      <c r="A6" s="1">
-        <v>4</v>
-      </c>
-      <c r="B6" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">南</t>
-        </is>
-      </c>
-      <c r="C6" s="2" t="inlineStr">
+    <row r="6" ht="56" customHeight="1">
+      <c r="B6" s="16" t="inlineStr">
+        <is>
+          <t xml:space="preserve">南</t>
+        </is>
+      </c>
+      <c r="C6" s="18" t="inlineStr">
         <is>
           <t xml:space="preserve">자</t>
         </is>
       </c>
-      <c r="D6" s="2"/>
-      <c r="E6" s="2"/>
-      <c r="F6" s="2"/>
-      <c r="G6" s="2"/>
-      <c r="H6" s="2"/>
-      <c r="I6" s="2"/>
-      <c r="J6" s="2"/>
-      <c r="K6" s="2"/>
-      <c r="L6" s="2"/>
-      <c r="M6" s="2"/>
-      <c r="N6" s="2"/>
-      <c r="O6" s="2"/>
-      <c r="P6" s="2"/>
-      <c r="Q6" s="2"/>
-    </row>
-    <row r="7" ht="30" customHeight="1">
-      <c r="A7" s="1">
-        <v>5</v>
-      </c>
-      <c r="B7" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">潕</t>
-        </is>
-      </c>
-      <c r="C7" s="2" t="inlineStr">
+      <c r="D6" s="16"/>
+      <c r="E6" s="18"/>
+      <c r="F6" s="16"/>
+      <c r="G6" s="18"/>
+      <c r="H6" s="16"/>
+      <c r="I6" s="18"/>
+      <c r="J6" s="16"/>
+      <c r="K6" s="18"/>
+      <c r="L6" s="16"/>
+      <c r="M6" s="18"/>
+      <c r="N6" s="16"/>
+      <c r="O6" s="18"/>
+      <c r="P6" s="16"/>
+      <c r="Q6" s="18"/>
+    </row>
+    <row r="7" ht="56" customHeight="1">
+      <c r="B7" s="16" t="inlineStr">
+        <is>
+          <t xml:space="preserve">潕</t>
+        </is>
+      </c>
+      <c r="C7" s="19" t="inlineStr">
         <is>
           <t xml:space="preserve">리</t>
         </is>
       </c>
-      <c r="D7" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">南</t>
-        </is>
-      </c>
-      <c r="E7" s="2" t="inlineStr">
+      <c r="D7" s="16" t="inlineStr">
+        <is>
+          <t xml:space="preserve">南</t>
+        </is>
+      </c>
+      <c r="E7" s="19" t="inlineStr">
         <is>
           <t xml:space="preserve">이</t>
         </is>
       </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">南</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
+      <c r="F7" s="16" t="inlineStr">
+        <is>
+          <t xml:space="preserve">南</t>
+        </is>
+      </c>
+      <c r="G7" s="19" t="inlineStr">
         <is>
           <t xml:space="preserve">서</t>
         </is>
       </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">·</t>
-        </is>
-      </c>
-      <c r="I7" s="2" t="inlineStr">
+      <c r="H7" s="16" t="inlineStr">
+        <is>
+          <t xml:space="preserve">·</t>
+        </is>
+      </c>
+      <c r="I7" s="19" t="inlineStr">
         <is>
           <t xml:space="preserve">정</t>
         </is>
       </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">潕</t>
-        </is>
-      </c>
-      <c r="K7" s="2" t="inlineStr">
+      <c r="J7" s="16" t="inlineStr">
+        <is>
+          <t xml:space="preserve">潕</t>
+        </is>
+      </c>
+      <c r="K7" s="19" t="inlineStr">
         <is>
           <t xml:space="preserve">지</t>
         </is>
       </c>
-      <c r="L7" s="2" t="inlineStr">
+      <c r="L7" s="16" t="inlineStr">
         <is>
           <t xml:space="preserve">姑</t>
         </is>
       </c>
-      <c r="M7" s="2" t="inlineStr">
+      <c r="M7" s="19" t="inlineStr">
         <is>
           <t xml:space="preserve">나</t>
         </is>
       </c>
-      <c r="N7" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">南</t>
-        </is>
-      </c>
-      <c r="O7" s="2" t="inlineStr">
+      <c r="N7" s="16" t="inlineStr">
+        <is>
+          <t xml:space="preserve">南</t>
+        </is>
+      </c>
+      <c r="O7" s="19" t="inlineStr">
         <is>
           <t xml:space="preserve">옥</t>
         </is>
       </c>
-      <c r="P7" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">南</t>
-        </is>
-      </c>
-      <c r="Q7" s="2" t="inlineStr">
+      <c r="P7" s="16" t="inlineStr">
+        <is>
+          <t xml:space="preserve">南</t>
+        </is>
+      </c>
+      <c r="Q7" s="19" t="inlineStr">
         <is>
           <t xml:space="preserve">머</t>
         </is>
       </c>
     </row>
-    <row r="8" ht="30" customHeight="1">
-      <c r="A8" s="1">
-        <v>6</v>
-      </c>
-      <c r="B8" s="2"/>
-      <c r="C8" s="2"/>
-      <c r="D8" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">潕</t>
-        </is>
-      </c>
-      <c r="E8" s="2"/>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">潕</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
+    <row r="8" ht="56" customHeight="1">
+      <c r="B8" s="16"/>
+      <c r="C8" s="20"/>
+      <c r="D8" s="16" t="inlineStr">
+        <is>
+          <t xml:space="preserve">潕</t>
+        </is>
+      </c>
+      <c r="E8" s="20"/>
+      <c r="F8" s="16" t="inlineStr">
+        <is>
+          <t xml:space="preserve">潕</t>
+        </is>
+      </c>
+      <c r="G8" s="20" t="inlineStr">
         <is>
           <t xml:space="preserve">를</t>
         </is>
       </c>
-      <c r="H8" s="2"/>
-      <c r="I8" s="2"/>
-      <c r="J8" s="2"/>
-      <c r="K8" s="2"/>
-      <c r="L8" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">南</t>
-        </is>
-      </c>
-      <c r="M8" s="2" t="inlineStr">
+      <c r="H8" s="16"/>
+      <c r="I8" s="20"/>
+      <c r="J8" s="16"/>
+      <c r="K8" s="20"/>
+      <c r="L8" s="16" t="inlineStr">
+        <is>
+          <t xml:space="preserve">南</t>
+        </is>
+      </c>
+      <c r="M8" s="20" t="inlineStr">
         <is>
           <t xml:space="preserve">는</t>
         </is>
       </c>
-      <c r="N8" s="2"/>
-      <c r="O8" s="2"/>
-      <c r="P8" s="2"/>
-      <c r="Q8" s="2"/>
-    </row>
-    <row r="9" ht="30" customHeight="1">
-      <c r="A9" s="1">
-        <v>7</v>
-      </c>
-      <c r="B9" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">潕</t>
-        </is>
-      </c>
-      <c r="C9" s="2" t="inlineStr">
+      <c r="N8" s="16"/>
+      <c r="O8" s="20"/>
+      <c r="P8" s="16"/>
+      <c r="Q8" s="20"/>
+    </row>
+    <row r="9" ht="56" customHeight="1">
+      <c r="B9" s="16" t="inlineStr">
+        <is>
+          <t xml:space="preserve">潕</t>
+        </is>
+      </c>
+      <c r="C9" s="18" t="inlineStr">
         <is>
           <t xml:space="preserve">글</t>
         </is>
       </c>
-      <c r="D9" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">潕</t>
-        </is>
-      </c>
-      <c r="E9" s="2" t="inlineStr">
+      <c r="D9" s="16" t="inlineStr">
+        <is>
+          <t xml:space="preserve">潕</t>
+        </is>
+      </c>
+      <c r="E9" s="18" t="inlineStr">
         <is>
           <t xml:space="preserve">어</t>
         </is>
       </c>
-      <c r="F9" s="2" t="inlineStr">
+      <c r="F9" s="16" t="inlineStr">
         <is>
           <t xml:space="preserve">姑</t>
         </is>
       </c>
-      <c r="G9" s="2"/>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">潕</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
+      <c r="G9" s="18"/>
+      <c r="H9" s="16" t="inlineStr">
+        <is>
+          <t xml:space="preserve">潕</t>
+        </is>
+      </c>
+      <c r="I9" s="18" t="inlineStr">
         <is>
           <t xml:space="preserve">내</t>
         </is>
       </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">潕</t>
-        </is>
-      </c>
-      <c r="K9" s="2" t="inlineStr">
+      <c r="J9" s="16" t="inlineStr">
+        <is>
+          <t xml:space="preserve">潕</t>
+        </is>
+      </c>
+      <c r="K9" s="18" t="inlineStr">
         <is>
           <t xml:space="preserve">고</t>
         </is>
       </c>
-      <c r="L9" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">潕</t>
-        </is>
-      </c>
-      <c r="M9" s="2" t="inlineStr">
+      <c r="L9" s="16" t="inlineStr">
+        <is>
+          <t xml:space="preserve">潕</t>
+        </is>
+      </c>
+      <c r="M9" s="18" t="inlineStr">
         <is>
           <t xml:space="preserve">것</t>
         </is>
       </c>
-      <c r="N9" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">潕</t>
-        </is>
-      </c>
-      <c r="O9" s="2" t="inlineStr">
+      <c r="N9" s="16" t="inlineStr">
+        <is>
+          <t xml:space="preserve">潕</t>
+        </is>
+      </c>
+      <c r="O9" s="18" t="inlineStr">
         <is>
           <t xml:space="preserve">방</t>
         </is>
       </c>
-      <c r="P9" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">南</t>
-        </is>
-      </c>
-      <c r="Q9" s="2" t="inlineStr">
+      <c r="P9" s="16" t="inlineStr">
+        <is>
+          <t xml:space="preserve">南</t>
+        </is>
+      </c>
+      <c r="Q9" s="18" t="inlineStr">
         <is>
           <t xml:space="preserve">리</t>
         </is>
       </c>
     </row>
-    <row r="10" ht="30" customHeight="1">
-      <c r="A10" s="1">
-        <v>8</v>
-      </c>
-      <c r="B10" s="2"/>
-      <c r="C10" s="2"/>
-      <c r="D10" s="2"/>
-      <c r="E10" s="2"/>
-      <c r="F10" s="2"/>
-      <c r="G10" s="2"/>
-      <c r="H10" s="2"/>
-      <c r="I10" s="2"/>
-      <c r="J10" s="2"/>
-      <c r="K10" s="2"/>
-      <c r="L10" s="2"/>
-      <c r="M10" s="2"/>
-      <c r="N10" s="2"/>
-      <c r="O10" s="2"/>
-      <c r="P10" s="2"/>
-      <c r="Q10" s="2"/>
-    </row>
-    <row r="11" ht="30" customHeight="1">
-      <c r="A11" s="1">
-        <v>9</v>
-      </c>
-      <c r="B11" s="2" t="inlineStr">
+    <row r="10" ht="56" customHeight="1">
+      <c r="B10" s="16"/>
+      <c r="C10" s="19"/>
+      <c r="D10" s="16"/>
+      <c r="E10" s="19"/>
+      <c r="F10" s="16"/>
+      <c r="G10" s="19"/>
+      <c r="H10" s="16"/>
+      <c r="I10" s="19"/>
+      <c r="J10" s="16"/>
+      <c r="K10" s="19"/>
+      <c r="L10" s="16"/>
+      <c r="M10" s="19"/>
+      <c r="N10" s="16"/>
+      <c r="O10" s="19"/>
+      <c r="P10" s="16"/>
+      <c r="Q10" s="19"/>
+    </row>
+    <row r="11" ht="56" customHeight="1">
+      <c r="B11" s="16" t="inlineStr">
         <is>
           <t xml:space="preserve">姑</t>
         </is>
       </c>
-      <c r="C11" s="2" t="inlineStr">
+      <c r="C11" s="20" t="inlineStr">
         <is>
           <t xml:space="preserve">못</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">·</t>
-        </is>
-      </c>
-      <c r="E11" s="2" t="inlineStr">
+      <c r="D11" s="16" t="inlineStr">
+        <is>
+          <t xml:space="preserve">·</t>
+        </is>
+      </c>
+      <c r="E11" s="20" t="inlineStr">
         <is>
           <t xml:space="preserve">는</t>
         </is>
       </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">南</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
+      <c r="F11" s="16" t="inlineStr">
+        <is>
+          <t xml:space="preserve">南</t>
+        </is>
+      </c>
+      <c r="G11" s="20" t="inlineStr">
         <is>
           <t xml:space="preserve">봉</t>
         </is>
       </c>
-      <c r="H11" s="2" t="inlineStr">
+      <c r="H11" s="16" t="inlineStr">
         <is>
           <t xml:space="preserve">姑</t>
         </is>
       </c>
-      <c r="I11" s="2" t="inlineStr">
+      <c r="I11" s="20" t="inlineStr">
         <is>
           <t xml:space="preserve">가</t>
         </is>
       </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">潕</t>
-        </is>
-      </c>
-      <c r="K11" s="2" t="inlineStr">
+      <c r="J11" s="16" t="inlineStr">
+        <is>
+          <t xml:space="preserve">潕</t>
+        </is>
+      </c>
+      <c r="K11" s="20" t="inlineStr">
         <is>
           <t xml:space="preserve">보</t>
         </is>
       </c>
-      <c r="L11" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">南</t>
-        </is>
-      </c>
-      <c r="M11" s="2" t="inlineStr">
+      <c r="L11" s="16" t="inlineStr">
+        <is>
+          <t xml:space="preserve">南</t>
+        </is>
+      </c>
+      <c r="M11" s="20" t="inlineStr">
         <is>
           <t xml:space="preserve">은</t>
         </is>
       </c>
-      <c r="N11" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">潕</t>
-        </is>
-      </c>
-      <c r="O11" s="2" t="inlineStr">
+      <c r="N11" s="16" t="inlineStr">
+        <is>
+          <t xml:space="preserve">潕</t>
+        </is>
+      </c>
+      <c r="O11" s="20" t="inlineStr">
         <is>
           <t xml:space="preserve">에</t>
         </is>
       </c>
-      <c r="P11" s="2"/>
-      <c r="Q11" s="2"/>
-    </row>
-    <row r="12" ht="30" customHeight="1">
-      <c r="A12" s="1">
-        <v>10</v>
-      </c>
-      <c r="B12" s="2" t="inlineStr">
+      <c r="P11" s="16"/>
+      <c r="Q11" s="20"/>
+    </row>
+    <row r="12" ht="56" customHeight="1">
+      <c r="B12" s="16" t="inlineStr">
         <is>
           <t xml:space="preserve">姑</t>
         </is>
       </c>
-      <c r="C12" s="2" t="inlineStr">
+      <c r="C12" s="18" t="inlineStr">
         <is>
           <t xml:space="preserve">어</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">潕</t>
-        </is>
-      </c>
-      <c r="E12" s="2" t="inlineStr">
+      <c r="D12" s="16" t="inlineStr">
+        <is>
+          <t xml:space="preserve">潕</t>
+        </is>
+      </c>
+      <c r="E12" s="18" t="inlineStr">
         <is>
           <t xml:space="preserve">가</t>
         </is>
       </c>
-      <c r="F12" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">南</t>
-        </is>
-      </c>
-      <c r="G12" s="2"/>
-      <c r="H12" s="2"/>
-      <c r="I12" s="2"/>
-      <c r="J12" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">潕</t>
-        </is>
-      </c>
-      <c r="K12" s="2"/>
-      <c r="L12" s="2"/>
-      <c r="M12" s="2"/>
-      <c r="N12" s="2"/>
-      <c r="O12" s="2"/>
-      <c r="P12" s="2"/>
-      <c r="Q12" s="2"/>
-    </row>
-    <row r="13" ht="30" customHeight="1">
-      <c r="A13" s="1">
-        <v>11</v>
-      </c>
-      <c r="B13" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">·</t>
-        </is>
-      </c>
-      <c r="C13" s="2"/>
-      <c r="D13" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">潕</t>
-        </is>
-      </c>
-      <c r="E13" s="2"/>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">·</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
+      <c r="F12" s="16" t="inlineStr">
+        <is>
+          <t xml:space="preserve">南</t>
+        </is>
+      </c>
+      <c r="G12" s="18"/>
+      <c r="H12" s="16"/>
+      <c r="I12" s="18"/>
+      <c r="J12" s="16" t="inlineStr">
+        <is>
+          <t xml:space="preserve">潕</t>
+        </is>
+      </c>
+      <c r="K12" s="18"/>
+      <c r="L12" s="16"/>
+      <c r="M12" s="18"/>
+      <c r="N12" s="16"/>
+      <c r="O12" s="18"/>
+      <c r="P12" s="16"/>
+      <c r="Q12" s="18"/>
+    </row>
+    <row r="13" ht="56" customHeight="1">
+      <c r="B13" s="16" t="inlineStr">
+        <is>
+          <t xml:space="preserve">·</t>
+        </is>
+      </c>
+      <c r="C13" s="19"/>
+      <c r="D13" s="16" t="inlineStr">
+        <is>
+          <t xml:space="preserve">潕</t>
+        </is>
+      </c>
+      <c r="E13" s="19"/>
+      <c r="F13" s="16" t="inlineStr">
+        <is>
+          <t xml:space="preserve">·</t>
+        </is>
+      </c>
+      <c r="G13" s="19" t="inlineStr">
         <is>
           <t xml:space="preserve">양</t>
         </is>
       </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">·</t>
-        </is>
-      </c>
-      <c r="I13" s="2"/>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">潕</t>
-        </is>
-      </c>
-      <c r="K13" s="2" t="inlineStr">
+      <c r="H13" s="16" t="inlineStr">
+        <is>
+          <t xml:space="preserve">·</t>
+        </is>
+      </c>
+      <c r="I13" s="19"/>
+      <c r="J13" s="16" t="inlineStr">
+        <is>
+          <t xml:space="preserve">潕</t>
+        </is>
+      </c>
+      <c r="K13" s="19" t="inlineStr">
         <is>
           <t xml:space="preserve">고</t>
         </is>
       </c>
-      <c r="L13" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">·</t>
-        </is>
-      </c>
-      <c r="M13" s="2"/>
-      <c r="N13" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">·</t>
-        </is>
-      </c>
-      <c r="O13" s="2"/>
-      <c r="P13" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">·</t>
-        </is>
-      </c>
-      <c r="Q13" s="2"/>
-    </row>
-    <row r="14" ht="30" customHeight="1">
-      <c r="A14" s="1">
-        <v>12</v>
-      </c>
-      <c r="B14" s="2" t="inlineStr">
+      <c r="L13" s="16" t="inlineStr">
+        <is>
+          <t xml:space="preserve">·</t>
+        </is>
+      </c>
+      <c r="M13" s="19"/>
+      <c r="N13" s="16" t="inlineStr">
+        <is>
+          <t xml:space="preserve">·</t>
+        </is>
+      </c>
+      <c r="O13" s="19"/>
+      <c r="P13" s="16" t="inlineStr">
+        <is>
+          <t xml:space="preserve">·</t>
+        </is>
+      </c>
+      <c r="Q13" s="19"/>
+    </row>
+    <row r="14" ht="56" customHeight="1">
+      <c r="B14" s="16" t="inlineStr">
         <is>
           <t xml:space="preserve">△</t>
         </is>
       </c>
-      <c r="C14" s="2"/>
-      <c r="D14" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">潕</t>
-        </is>
-      </c>
-      <c r="E14" s="2"/>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">·</t>
-        </is>
-      </c>
-      <c r="G14" s="2"/>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">·</t>
-        </is>
-      </c>
-      <c r="I14" s="2"/>
-      <c r="J14" s="2"/>
-      <c r="K14" s="2"/>
-      <c r="L14" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">·</t>
-        </is>
-      </c>
-      <c r="M14" s="2"/>
-      <c r="N14" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">·</t>
-        </is>
-      </c>
-      <c r="O14" s="2"/>
-      <c r="P14" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">·</t>
-        </is>
-      </c>
-      <c r="Q14" s="2"/>
+      <c r="C14" s="20"/>
+      <c r="D14" s="16" t="inlineStr">
+        <is>
+          <t xml:space="preserve">潕</t>
+        </is>
+      </c>
+      <c r="E14" s="20"/>
+      <c r="F14" s="16" t="inlineStr">
+        <is>
+          <t xml:space="preserve">·</t>
+        </is>
+      </c>
+      <c r="G14" s="20"/>
+      <c r="H14" s="16" t="inlineStr">
+        <is>
+          <t xml:space="preserve">·</t>
+        </is>
+      </c>
+      <c r="I14" s="20"/>
+      <c r="J14" s="16"/>
+      <c r="K14" s="20"/>
+      <c r="L14" s="16" t="inlineStr">
+        <is>
+          <t xml:space="preserve">·</t>
+        </is>
+      </c>
+      <c r="M14" s="20"/>
+      <c r="N14" s="16" t="inlineStr">
+        <is>
+          <t xml:space="preserve">·</t>
+        </is>
+      </c>
+      <c r="O14" s="20"/>
+      <c r="P14" s="16" t="inlineStr">
+        <is>
+          <t xml:space="preserve">·</t>
+        </is>
+      </c>
+      <c r="Q14" s="20"/>
+    </row>
+    <row r="15"/>
+    <row r="16" ht="60" customHeight="1">
+      <c s="8" t="inlineStr" r="B16">
+        <is>
+          <t xml:space="preserve">쑥대머리</t>
+        </is>
+      </c>
+      <c s="8" r="C16"/>
+      <c s="8" r="D16"/>
+      <c s="8" r="E16"/>
+      <c s="8" r="F16"/>
+      <c s="8" r="G16"/>
+      <c s="8" r="H16"/>
+      <c s="8" r="I16"/>
+      <c s="8" r="J16"/>
+      <c s="8" r="K16"/>
+      <c s="8" r="L16"/>
+      <c s="8" r="M16"/>
+      <c s="8" r="N16"/>
+      <c s="8" r="O16"/>
+      <c s="8" r="P16"/>
+      <c s="8" r="Q16"/>
+    </row>
+    <row r="17" ht="56" customHeight="1">
+      <c r="B17" s="17"/>
+      <c r="C17" s="21"/>
+      <c r="D17" s="17"/>
+      <c r="E17" s="21"/>
+      <c r="F17" s="17"/>
+      <c r="G17" s="21"/>
+      <c r="H17" s="16" t="inlineStr">
+        <is>
+          <t xml:space="preserve">南</t>
+        </is>
+      </c>
+      <c r="I17" s="18" t="inlineStr">
+        <is>
+          <t xml:space="preserve">앵</t>
+        </is>
+      </c>
+      <c r="J17" s="16" t="inlineStr">
+        <is>
+          <t xml:space="preserve">南</t>
+        </is>
+      </c>
+      <c r="K17" s="18" t="inlineStr">
+        <is>
+          <t xml:space="preserve">막</t>
+        </is>
+      </c>
+      <c r="L17" s="16" t="inlineStr">
+        <is>
+          <t xml:space="preserve">南</t>
+        </is>
+      </c>
+      <c r="M17" s="18" t="inlineStr">
+        <is>
+          <t xml:space="preserve">번</t>
+        </is>
+      </c>
+      <c r="N17" s="16" t="inlineStr">
+        <is>
+          <t xml:space="preserve">姑</t>
+        </is>
+      </c>
+      <c r="O17" s="18" t="inlineStr">
+        <is>
+          <t xml:space="preserve">계</t>
+        </is>
+      </c>
+      <c r="P17" s="16" t="inlineStr">
+        <is>
+          <t xml:space="preserve">潕</t>
+        </is>
+      </c>
+      <c r="Q17" s="18" t="inlineStr">
+        <is>
+          <t xml:space="preserve">예</t>
+        </is>
+      </c>
+    </row>
+    <row r="18" ht="56" customHeight="1">
+      <c r="B18" s="17"/>
+      <c r="C18" s="22"/>
+      <c r="D18" s="17"/>
+      <c r="E18" s="22"/>
+      <c r="F18" s="17"/>
+      <c r="G18" s="22"/>
+      <c r="H18" s="16" t="inlineStr">
+        <is>
+          <t xml:space="preserve">潕</t>
+        </is>
+      </c>
+      <c r="I18" s="19" t="inlineStr">
+        <is>
+          <t xml:space="preserve">무</t>
+        </is>
+      </c>
+      <c r="J18" s="16" t="inlineStr">
+        <is>
+          <t xml:space="preserve">·</t>
+        </is>
+      </c>
+      <c r="K18" s="19" t="inlineStr">
+        <is>
+          <t xml:space="preserve">왕</t>
+        </is>
+      </c>
+      <c r="L18" s="16"/>
+      <c r="M18" s="19"/>
+      <c r="N18" s="16" t="inlineStr">
+        <is>
+          <t xml:space="preserve">南</t>
+        </is>
+      </c>
+      <c r="O18" s="19" t="inlineStr">
+        <is>
+          <t xml:space="preserve">궁</t>
+        </is>
+      </c>
+      <c r="P18" s="16" t="inlineStr">
+        <is>
+          <t xml:space="preserve">潕</t>
+        </is>
+      </c>
+      <c r="Q18" s="19" t="inlineStr">
+        <is>
+          <t xml:space="preserve">의</t>
+        </is>
+      </c>
+    </row>
+    <row r="19" ht="56" customHeight="1">
+      <c r="B19" s="17"/>
+      <c r="C19" s="23"/>
+      <c r="D19" s="17"/>
+      <c r="E19" s="23"/>
+      <c r="F19" s="17"/>
+      <c r="G19" s="23"/>
+      <c r="H19" s="16" t="inlineStr">
+        <is>
+          <t xml:space="preserve">潕</t>
+        </is>
+      </c>
+      <c r="I19" s="20" t="inlineStr">
+        <is>
+          <t xml:space="preserve">서</t>
+        </is>
+      </c>
+      <c r="J19" s="16" t="inlineStr">
+        <is>
+          <t xml:space="preserve">·</t>
+        </is>
+      </c>
+      <c r="K19" s="20" t="inlineStr">
+        <is>
+          <t xml:space="preserve">막</t>
+        </is>
+      </c>
+      <c r="L19" s="16" t="inlineStr">
+        <is>
+          <t xml:space="preserve">·</t>
+        </is>
+      </c>
+      <c r="M19" s="20" t="inlineStr">
+        <is>
+          <t xml:space="preserve">듯</t>
+        </is>
+      </c>
+      <c r="N19" s="16" t="inlineStr">
+        <is>
+          <t xml:space="preserve">南</t>
+        </is>
+      </c>
+      <c r="O19" s="20" t="inlineStr">
+        <is>
+          <t xml:space="preserve">항</t>
+        </is>
+      </c>
+      <c r="P19" s="16" t="inlineStr">
+        <is>
+          <t xml:space="preserve">潕</t>
+        </is>
+      </c>
+      <c r="Q19" s="20" t="inlineStr">
+        <is>
+          <t xml:space="preserve">신</t>
+        </is>
+      </c>
+    </row>
+    <row r="20" ht="56" customHeight="1">
+      <c r="B20" s="17"/>
+      <c r="C20" s="21"/>
+      <c r="D20" s="17"/>
+      <c r="E20" s="21"/>
+      <c r="F20" s="17"/>
+      <c r="G20" s="21"/>
+      <c r="H20" s="16" t="inlineStr">
+        <is>
+          <t xml:space="preserve">無</t>
+        </is>
+      </c>
+      <c r="I20" s="18" t="inlineStr">
+        <is>
+          <t xml:space="preserve">를</t>
+        </is>
+      </c>
+      <c r="J20" s="16" t="inlineStr">
+        <is>
+          <t xml:space="preserve">△</t>
+        </is>
+      </c>
+      <c r="K20" s="18" t="inlineStr">
+        <is>
+          <t xml:space="preserve">래</t>
+        </is>
+      </c>
+      <c r="L20" s="16" t="inlineStr">
+        <is>
+          <t xml:space="preserve">潕</t>
+        </is>
+      </c>
+      <c r="M20" s="18" t="inlineStr">
+        <is>
+          <t xml:space="preserve">이</t>
+        </is>
+      </c>
+      <c r="N20" s="16" t="inlineStr">
+        <is>
+          <t xml:space="preserve">·</t>
+        </is>
+      </c>
+      <c r="O20" s="18" t="inlineStr">
+        <is>
+          <t xml:space="preserve">아</t>
+        </is>
+      </c>
+      <c r="P20" s="16" t="inlineStr">
+        <is>
+          <t xml:space="preserve">·</t>
+        </is>
+      </c>
+      <c r="Q20" s="18"/>
+    </row>
+    <row r="21" ht="56" customHeight="1">
+      <c r="B21" s="17"/>
+      <c r="C21" s="22"/>
+      <c r="D21" s="17"/>
+      <c r="E21" s="22"/>
+      <c r="F21" s="17"/>
+      <c r="G21" s="22"/>
+      <c r="H21" s="16" t="inlineStr">
+        <is>
+          <t xml:space="preserve">南</t>
+        </is>
+      </c>
+      <c r="I21" s="19" t="inlineStr">
+        <is>
+          <t xml:space="preserve">을</t>
+        </is>
+      </c>
+      <c r="J21" s="16" t="inlineStr">
+        <is>
+          <t xml:space="preserve">潕</t>
+        </is>
+      </c>
+      <c r="K21" s="19"/>
+      <c r="L21" s="16" t="inlineStr">
+        <is>
+          <t xml:space="preserve">無</t>
+        </is>
+      </c>
+      <c r="M21" s="19"/>
+      <c r="N21" s="16" t="inlineStr">
+        <is>
+          <t xml:space="preserve">·</t>
+        </is>
+      </c>
+      <c r="O21" s="19"/>
+      <c r="P21" s="16" t="inlineStr">
+        <is>
+          <t xml:space="preserve">·</t>
+        </is>
+      </c>
+      <c r="Q21" s="19"/>
+    </row>
+    <row r="22" ht="56" customHeight="1">
+      <c r="B22" s="17"/>
+      <c r="C22" s="23"/>
+      <c r="D22" s="17"/>
+      <c r="E22" s="23"/>
+      <c r="F22" s="17"/>
+      <c r="G22" s="23"/>
+      <c r="H22" s="16" t="inlineStr">
+        <is>
+          <t xml:space="preserve">潕</t>
+        </is>
+      </c>
+      <c r="I22" s="20" t="inlineStr">
+        <is>
+          <t xml:space="preserve">네</t>
+        </is>
+      </c>
+      <c r="J22" s="16" t="inlineStr">
+        <is>
+          <t xml:space="preserve">潕</t>
+        </is>
+      </c>
+      <c r="K22" s="20" t="inlineStr">
+        <is>
+          <t xml:space="preserve">못</t>
+        </is>
+      </c>
+      <c r="L22" s="16" t="inlineStr">
+        <is>
+          <t xml:space="preserve">南</t>
+        </is>
+      </c>
+      <c r="M22" s="20" t="inlineStr">
+        <is>
+          <t xml:space="preserve">솟</t>
+        </is>
+      </c>
+      <c r="N22" s="16"/>
+      <c r="O22" s="20"/>
+      <c r="P22" s="16" t="inlineStr">
+        <is>
+          <t xml:space="preserve">潕</t>
+        </is>
+      </c>
+      <c r="Q22" s="20" t="inlineStr">
+        <is>
+          <t xml:space="preserve">술</t>
+        </is>
+      </c>
+    </row>
+    <row r="23" ht="56" customHeight="1">
+      <c r="B23" s="17"/>
+      <c r="C23" s="21"/>
+      <c r="D23" s="17"/>
+      <c r="E23" s="21"/>
+      <c r="F23" s="17"/>
+      <c r="G23" s="21"/>
+      <c r="H23" s="16" t="inlineStr">
+        <is>
+          <t xml:space="preserve">姑</t>
+        </is>
+      </c>
+      <c r="I23" s="18" t="inlineStr">
+        <is>
+          <t xml:space="preserve">가</t>
+        </is>
+      </c>
+      <c r="J23" s="16" t="inlineStr">
+        <is>
+          <t xml:space="preserve">南</t>
+        </is>
+      </c>
+      <c r="K23" s="18" t="inlineStr">
+        <is>
+          <t xml:space="preserve">봤</t>
+        </is>
+      </c>
+      <c r="L23" s="16" t="inlineStr">
+        <is>
+          <t xml:space="preserve">姑</t>
+        </is>
+      </c>
+      <c r="M23" s="18" t="inlineStr">
+        <is>
+          <t xml:space="preserve">아</t>
+        </is>
+      </c>
+      <c r="N23" s="16" t="inlineStr">
+        <is>
+          <t xml:space="preserve">姑</t>
+        </is>
+      </c>
+      <c r="O23" s="18"/>
+      <c r="P23" s="16" t="inlineStr">
+        <is>
+          <t xml:space="preserve">南</t>
+        </is>
+      </c>
+      <c r="Q23" s="18" t="inlineStr">
+        <is>
+          <t xml:space="preserve">금</t>
+        </is>
+      </c>
+    </row>
+    <row r="24" ht="56" customHeight="1">
+      <c r="B24" s="17"/>
+      <c r="C24" s="22"/>
+      <c r="D24" s="17"/>
+      <c r="E24" s="22"/>
+      <c r="F24" s="17"/>
+      <c r="G24" s="22"/>
+      <c r="H24" s="16" t="inlineStr">
+        <is>
+          <t xml:space="preserve">姑</t>
+        </is>
+      </c>
+      <c r="I24" s="19"/>
+      <c r="J24" s="16" t="inlineStr">
+        <is>
+          <t xml:space="preserve">·</t>
+        </is>
+      </c>
+      <c r="K24" s="19"/>
+      <c r="L24" s="16" t="inlineStr">
+        <is>
+          <t xml:space="preserve">姑</t>
+        </is>
+      </c>
+      <c r="M24" s="19"/>
+      <c r="N24" s="16" t="inlineStr">
+        <is>
+          <t xml:space="preserve">姑</t>
+        </is>
+      </c>
+      <c r="O24" s="19"/>
+      <c r="P24" s="16" t="inlineStr">
+        <is>
+          <t xml:space="preserve">·</t>
+        </is>
+      </c>
+      <c r="Q24" s="19"/>
+    </row>
+    <row r="25" ht="56" customHeight="1">
+      <c r="B25" s="17"/>
+      <c r="C25" s="23"/>
+      <c r="D25" s="17"/>
+      <c r="E25" s="23"/>
+      <c r="F25" s="17"/>
+      <c r="G25" s="23"/>
+      <c r="H25" s="16" t="inlineStr">
+        <is>
+          <t xml:space="preserve">南</t>
+        </is>
+      </c>
+      <c r="I25" s="20"/>
+      <c r="J25" s="16" t="inlineStr">
+        <is>
+          <t xml:space="preserve">姑</t>
+        </is>
+      </c>
+      <c r="K25" s="20" t="inlineStr">
+        <is>
+          <t xml:space="preserve">어</t>
+        </is>
+      </c>
+      <c r="L25" s="16" t="inlineStr">
+        <is>
+          <t xml:space="preserve">南</t>
+        </is>
+      </c>
+      <c r="M25" s="20"/>
+      <c r="N25" s="16" t="inlineStr">
+        <is>
+          <t xml:space="preserve">南</t>
+        </is>
+      </c>
+      <c r="O25" s="20"/>
+      <c r="P25" s="16"/>
+      <c r="Q25" s="20"/>
+    </row>
+    <row r="26" ht="56" customHeight="1">
+      <c r="B26" s="17"/>
+      <c r="C26" s="21"/>
+      <c r="D26" s="17"/>
+      <c r="E26" s="21"/>
+      <c r="F26" s="17"/>
+      <c r="G26" s="21"/>
+      <c r="H26" s="16" t="inlineStr">
+        <is>
+          <t xml:space="preserve">南</t>
+        </is>
+      </c>
+      <c r="I26" s="18"/>
+      <c r="J26" s="16" t="inlineStr">
+        <is>
+          <t xml:space="preserve">姑</t>
+        </is>
+      </c>
+      <c r="K26" s="18" t="inlineStr">
+        <is>
+          <t xml:space="preserve">네</t>
+        </is>
+      </c>
+      <c r="L26" s="16" t="inlineStr">
+        <is>
+          <t xml:space="preserve">南</t>
+        </is>
+      </c>
+      <c r="M26" s="18"/>
+      <c r="N26" s="16" t="inlineStr">
+        <is>
+          <t xml:space="preserve">·</t>
+        </is>
+      </c>
+      <c r="O26" s="18"/>
+      <c r="P26" s="16" t="inlineStr">
+        <is>
+          <t xml:space="preserve">潕</t>
+        </is>
+      </c>
+      <c r="Q26" s="18" t="inlineStr">
+        <is>
+          <t xml:space="preserve">슬</t>
+        </is>
+      </c>
+    </row>
+    <row r="27" ht="56" customHeight="1">
+      <c r="B27" s="17"/>
+      <c r="C27" s="22"/>
+      <c r="D27" s="17"/>
+      <c r="E27" s="22"/>
+      <c r="F27" s="17"/>
+      <c r="G27" s="22"/>
+      <c r="H27" s="16" t="inlineStr">
+        <is>
+          <t xml:space="preserve">·</t>
+        </is>
+      </c>
+      <c r="I27" s="19"/>
+      <c r="J27" s="16" t="inlineStr">
+        <is>
+          <t xml:space="preserve">·</t>
+        </is>
+      </c>
+      <c r="K27" s="19"/>
+      <c r="L27" s="16" t="inlineStr">
+        <is>
+          <t xml:space="preserve">·</t>
+        </is>
+      </c>
+      <c r="M27" s="19"/>
+      <c r="N27" s="16" t="inlineStr">
+        <is>
+          <t xml:space="preserve">·</t>
+        </is>
+      </c>
+      <c r="O27" s="19"/>
+      <c r="P27" s="16" t="inlineStr">
+        <is>
+          <t xml:space="preserve">姑</t>
+        </is>
+      </c>
+      <c r="Q27" s="19"/>
+    </row>
+    <row r="28" ht="56" customHeight="1">
+      <c r="B28" s="17"/>
+      <c r="C28" s="23"/>
+      <c r="D28" s="17"/>
+      <c r="E28" s="23"/>
+      <c r="F28" s="17"/>
+      <c r="G28" s="23"/>
+      <c r="H28" s="16" t="inlineStr">
+        <is>
+          <t xml:space="preserve">△</t>
+        </is>
+      </c>
+      <c r="I28" s="20"/>
+      <c r="J28" s="16" t="inlineStr">
+        <is>
+          <t xml:space="preserve">△</t>
+        </is>
+      </c>
+      <c r="K28" s="20"/>
+      <c r="L28" s="16" t="inlineStr">
+        <is>
+          <t xml:space="preserve">△</t>
+        </is>
+      </c>
+      <c r="M28" s="20"/>
+      <c r="N28" s="16" t="inlineStr">
+        <is>
+          <t xml:space="preserve">△</t>
+        </is>
+      </c>
+      <c r="O28" s="20"/>
+      <c r="P28" s="16" t="inlineStr">
+        <is>
+          <t xml:space="preserve">潕</t>
+        </is>
+      </c>
+      <c r="Q28" s="20"/>
     </row>
   </sheetData>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <cols>
-    <col min="1" max="1" width="6" customWidth="1"/>
-    <col min="2" max="2" width="9" customWidth="1"/>
-    <col min="3" max="3" width="6" customWidth="1"/>
-    <col min="4" max="4" width="9" customWidth="1"/>
-    <col min="5" max="5" width="6" customWidth="1"/>
-    <col min="6" max="6" width="9" customWidth="1"/>
-    <col min="7" max="7" width="6" customWidth="1"/>
-    <col min="8" max="8" width="9" customWidth="1"/>
-    <col min="9" max="9" width="6" customWidth="1"/>
-    <col min="10" max="10" width="9" customWidth="1"/>
-    <col min="11" max="11" width="6" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1">
-      <c r="A1" s="6" t="inlineStr">
-        <is>
-          <t xml:space="preserve">쑥대머리 — 민요채보-1/쑥대머리-2.png</t>
-        </is>
-      </c>
-      <c r="B1" s="6"/>
-      <c r="C1" s="6"/>
-      <c r="D1" s="6"/>
-      <c r="E1" s="6"/>
-      <c r="F1" s="6"/>
-      <c r="G1" s="6"/>
-      <c r="H1" s="6"/>
-      <c r="I1" s="6"/>
-      <c r="J1" s="6"/>
-      <c r="K1" s="6"/>
-    </row>
-    <row r="2">
-      <c r="A2" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">정간</t>
-        </is>
-      </c>
-      <c r="B2" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">5줄</t>
-        </is>
-      </c>
-      <c r="C2" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">가사</t>
-        </is>
-      </c>
-      <c r="D2" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">4줄</t>
-        </is>
-      </c>
-      <c r="E2" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">가사</t>
-        </is>
-      </c>
-      <c r="F2" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">3줄</t>
-        </is>
-      </c>
-      <c r="G2" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">가사</t>
-        </is>
-      </c>
-      <c r="H2" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">2줄</t>
-        </is>
-      </c>
-      <c r="I2" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">가사</t>
-        </is>
-      </c>
-      <c r="J2" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1줄</t>
-        </is>
-      </c>
-      <c r="K2" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">가사</t>
-        </is>
-      </c>
-    </row>
-    <row r="3" ht="30" customHeight="1">
-      <c r="A3" s="1">
-        <v>1</v>
-      </c>
-      <c r="B3" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">南</t>
-        </is>
-      </c>
-      <c r="C3" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">앵</t>
-        </is>
-      </c>
-      <c r="D3" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">南</t>
-        </is>
-      </c>
-      <c r="E3" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">막</t>
-        </is>
-      </c>
-      <c r="F3" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">南</t>
-        </is>
-      </c>
-      <c r="G3" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">번</t>
-        </is>
-      </c>
-      <c r="H3" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">姑</t>
-        </is>
-      </c>
-      <c r="I3" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">계</t>
-        </is>
-      </c>
-      <c r="J3" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">潕</t>
-        </is>
-      </c>
-      <c r="K3" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">예</t>
-        </is>
-      </c>
-    </row>
-    <row r="4" ht="30" customHeight="1">
-      <c r="A4" s="1">
-        <v>2</v>
-      </c>
-      <c r="B4" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">潕</t>
-        </is>
-      </c>
-      <c r="C4" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">무</t>
-        </is>
-      </c>
-      <c r="D4" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">·</t>
-        </is>
-      </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">왕</t>
-        </is>
-      </c>
-      <c r="F4" s="2"/>
-      <c r="G4" s="2"/>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">南</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">궁</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">潕</t>
-        </is>
-      </c>
-      <c r="K4" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">의</t>
-        </is>
-      </c>
-    </row>
-    <row r="5" ht="30" customHeight="1">
-      <c r="A5" s="1">
-        <v>3</v>
-      </c>
-      <c r="B5" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">潕</t>
-        </is>
-      </c>
-      <c r="C5" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">서</t>
-        </is>
-      </c>
-      <c r="D5" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">·</t>
-        </is>
-      </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">막</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">·</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">듯</t>
-        </is>
-      </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">南</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">항</t>
-        </is>
-      </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">潕</t>
-        </is>
-      </c>
-      <c r="K5" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">신</t>
-        </is>
-      </c>
-    </row>
-    <row r="6" ht="30" customHeight="1">
-      <c r="A6" s="1">
-        <v>4</v>
-      </c>
-      <c r="B6" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">無</t>
-        </is>
-      </c>
-      <c r="C6" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">를</t>
-        </is>
-      </c>
-      <c r="D6" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">△</t>
-        </is>
-      </c>
-      <c r="E6" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">래</t>
-        </is>
-      </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">潕</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">이</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">·</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">아</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">·</t>
-        </is>
-      </c>
-      <c r="K6" s="2"/>
-    </row>
-    <row r="7" ht="30" customHeight="1">
-      <c r="A7" s="1">
-        <v>5</v>
-      </c>
-      <c r="B7" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">南</t>
-        </is>
-      </c>
-      <c r="C7" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">을</t>
-        </is>
-      </c>
-      <c r="D7" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">潕</t>
-        </is>
-      </c>
-      <c r="E7" s="2"/>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">無</t>
-        </is>
-      </c>
-      <c r="G7" s="2"/>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">·</t>
-        </is>
-      </c>
-      <c r="I7" s="2"/>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">·</t>
-        </is>
-      </c>
-      <c r="K7" s="2"/>
-    </row>
-    <row r="8" ht="30" customHeight="1">
-      <c r="A8" s="1">
-        <v>6</v>
-      </c>
-      <c r="B8" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">潕</t>
-        </is>
-      </c>
-      <c r="C8" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">네</t>
-        </is>
-      </c>
-      <c r="D8" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">潕</t>
-        </is>
-      </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">못</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">南</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">솟</t>
-        </is>
-      </c>
-      <c r="H8" s="2"/>
-      <c r="I8" s="2"/>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">潕</t>
-        </is>
-      </c>
-      <c r="K8" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">술</t>
-        </is>
-      </c>
-    </row>
-    <row r="9" ht="30" customHeight="1">
-      <c r="A9" s="1">
-        <v>7</v>
-      </c>
-      <c r="B9" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">姑</t>
-        </is>
-      </c>
-      <c r="C9" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">가</t>
-        </is>
-      </c>
-      <c r="D9" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">南</t>
-        </is>
-      </c>
-      <c r="E9" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">봤</t>
-        </is>
-      </c>
-      <c r="F9" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">姑</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">아</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">姑</t>
-        </is>
-      </c>
-      <c r="I9" s="2"/>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">南</t>
-        </is>
-      </c>
-      <c r="K9" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">금</t>
-        </is>
-      </c>
-    </row>
-    <row r="10" ht="30" customHeight="1">
-      <c r="A10" s="1">
-        <v>8</v>
-      </c>
-      <c r="B10" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">姑</t>
-        </is>
-      </c>
-      <c r="C10" s="2"/>
-      <c r="D10" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">·</t>
-        </is>
-      </c>
-      <c r="E10" s="2"/>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">姑</t>
-        </is>
-      </c>
-      <c r="G10" s="2"/>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">姑</t>
-        </is>
-      </c>
-      <c r="I10" s="2"/>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">·</t>
-        </is>
-      </c>
-      <c r="K10" s="2"/>
-    </row>
-    <row r="11" ht="30" customHeight="1">
-      <c r="A11" s="1">
-        <v>9</v>
-      </c>
-      <c r="B11" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">南</t>
-        </is>
-      </c>
-      <c r="C11" s="2"/>
-      <c r="D11" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">姑</t>
-        </is>
-      </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">어</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">南</t>
-        </is>
-      </c>
-      <c r="G11" s="2"/>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">南</t>
-        </is>
-      </c>
-      <c r="I11" s="2"/>
-      <c r="J11" s="2"/>
-      <c r="K11" s="2"/>
-    </row>
-    <row r="12" ht="30" customHeight="1">
-      <c r="A12" s="1">
-        <v>10</v>
-      </c>
-      <c r="B12" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">南</t>
-        </is>
-      </c>
-      <c r="C12" s="2"/>
-      <c r="D12" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">姑</t>
-        </is>
-      </c>
-      <c r="E12" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">네</t>
-        </is>
-      </c>
-      <c r="F12" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">南</t>
-        </is>
-      </c>
-      <c r="G12" s="2"/>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">·</t>
-        </is>
-      </c>
-      <c r="I12" s="2"/>
-      <c r="J12" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">潕</t>
-        </is>
-      </c>
-      <c r="K12" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">슬</t>
-        </is>
-      </c>
-    </row>
-    <row r="13" ht="30" customHeight="1">
-      <c r="A13" s="1">
-        <v>11</v>
-      </c>
-      <c r="B13" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">·</t>
-        </is>
-      </c>
-      <c r="C13" s="2"/>
-      <c r="D13" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">·</t>
-        </is>
-      </c>
-      <c r="E13" s="2"/>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">·</t>
-        </is>
-      </c>
-      <c r="G13" s="2"/>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">·</t>
-        </is>
-      </c>
-      <c r="I13" s="2"/>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">姑</t>
-        </is>
-      </c>
-      <c r="K13" s="2"/>
-    </row>
-    <row r="14" ht="30" customHeight="1">
-      <c r="A14" s="1">
-        <v>12</v>
-      </c>
-      <c r="B14" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">△</t>
-        </is>
-      </c>
-      <c r="C14" s="2"/>
-      <c r="D14" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">△</t>
-        </is>
-      </c>
-      <c r="E14" s="2"/>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">△</t>
-        </is>
-      </c>
-      <c r="G14" s="2"/>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">△</t>
-        </is>
-      </c>
-      <c r="I14" s="2"/>
-      <c r="J14" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">潕</t>
-        </is>
-      </c>
-      <c r="K14" s="2"/>
-    </row>
-  </sheetData>
+  <mergeCells count="2">
+    <mergeCell ref="B2:Q2"/>
+    <mergeCell ref="B16:Q16"/>
+  </mergeCells>
+  <printOptions horizontalCentered="1"/>
+  <pageMargins left="0.4" right="0.4" top="0.5" bottom="0.5" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" fitToWidth="1" fitToHeight="0" scale="76"/>
+  <rowBreaks count="1" manualBreakCount="1">
+    <brk id="14" max="16383" man="1"/>
+  </rowBreaks>
 </worksheet>
 </file>